--- a/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6fd291eb5b854dd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R42de3fbb80144a1a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R42de3fbb80144a1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra925e8a7295947b2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra925e8a7295947b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rae90b15d781d4ac3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rae90b15d781d4ac3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R52f9890238c84bb5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R52f9890238c84bb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R195f7f6034f942e9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R195f7f6034f942e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5a1224ecaa764121"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5a1224ecaa764121"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R606250eea8b44fe9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R606250eea8b44fe9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R781ee4a308e6417e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R781ee4a308e6417e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5dff1e980c4248ee"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5dff1e980c4248ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra31ba11d25e6488f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra31ba11d25e6488f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re5deb7bc357e450b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re5deb7bc357e450b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra3ef0ca74acd44ba"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra3ef0ca74acd44ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1a476060db4a4bae"/>
   </x:sheets>
 </x:workbook>
 </file>
